--- a/PhanCong_phase 1_TamThaiTu.xlsx
+++ b/PhanCong_phase 1_TamThaiTu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOQ\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D59787-17DF-4100-BEB3-D70DFEC1BDCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC2E183-8DBC-4A40-8320-761291E41BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="58">
   <si>
     <t>IronPulse — Bảng Phân Công Đồ Án INT1313</t>
   </si>
@@ -123,16 +123,10 @@
     <t>Dùng Python (matplotlib) vẽ sơ đồ EER chuẩn Elmasri-Navathe. Style: lavender table, 3 cột dtype|attr|key</t>
   </si>
   <si>
-    <t>File: EER_IronPulse_v3.png</t>
-  </si>
-  <si>
     <t>Tổng hợp báo cáo Phase 1 (Word)</t>
   </si>
   <si>
     <t>Viết báo cáo đầy đủ 2 chương (Chương 1 + Chương 2.1) theo chuẩn đề cương</t>
-  </si>
-  <si>
-    <t>File: IronPulse_Phase1_Report.docx</t>
   </si>
   <si>
     <t>THỐNG KÊ PHÂN CÔNG — NHÓM TAM THÁI TỬ</t>
@@ -1010,9 +1004,7 @@
       <c r="H9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>31</v>
-      </c>
+      <c r="I9" s="8"/>
     </row>
     <row r="10" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
@@ -1022,10 +1014,10 @@
         <v>11</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>21</v>
@@ -1039,9 +1031,7 @@
       <c r="H10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="I10" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1087,7 +1077,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -1095,13 +1085,13 @@
     </row>
     <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -1115,7 +1105,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D3" s="12"/>
     </row>
@@ -1127,7 +1117,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D4" s="14"/>
     </row>
@@ -1139,7 +1129,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D5" s="12"/>
     </row>
@@ -1151,7 +1141,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D6" s="14"/>
     </row>
@@ -1173,7 +1163,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1181,22 +1171,22 @@
     </row>
     <row r="3" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1204,17 +1194,17 @@
     </row>
     <row r="8" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1222,17 +1212,17 @@
     </row>
     <row r="12" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1240,17 +1230,17 @@
     </row>
     <row r="16" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1258,32 +1248,32 @@
     </row>
     <row r="20" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
